--- a/Result/profitability/5013.xlsx
+++ b/Result/profitability/5013.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>0.43125</v>
+        <v>0.49125</v>
       </c>
       <c r="N2" t="n">
-        <v>12.3125</v>
+        <v>12.76125</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -681,16 +681,16 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>1.53</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.64375</v>
       </c>
       <c r="N3" t="n">
-        <v>13.065</v>
+        <v>13.67</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>1.15</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6649999999999999</v>
+        <v>0.73625</v>
       </c>
       <c r="N4" t="n">
-        <v>13.58</v>
+        <v>14.02875</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-2.43</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3100000000000001</v>
+        <v>0.405</v>
       </c>
       <c r="N5" t="n">
-        <v>7.96625</v>
+        <v>8.484999999999999</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.68</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1975</v>
+        <v>0.26875</v>
       </c>
       <c r="N6" t="n">
-        <v>5.098750000000001</v>
+        <v>5.4375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.55</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0775</v>
+        <v>0.14875</v>
       </c>
       <c r="N7" t="n">
-        <v>3.17625</v>
+        <v>3.52875</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.23</v>
       </c>
       <c r="M8" t="n">
-        <v>0.05500000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="N8" t="n">
-        <v>3.11875</v>
+        <v>3.6675</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1521,7 +1521,7 @@
         <v>0.05875</v>
       </c>
       <c r="N9" t="n">
-        <v>2.936250000000001</v>
+        <v>2.93625</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
@@ -1775,7 +1775,7 @@
         <v>-0.05500000000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>2.010000000000001</v>
+        <v>2.01</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -1902,7 +1902,7 @@
         <v>-0.08750000000000004</v>
       </c>
       <c r="N12" t="n">
-        <v>1.605000000000001</v>
+        <v>1.605</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5013</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2245</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1889</v>
+      </c>
+      <c r="E75" t="n">
+        <v>356</v>
+      </c>
+      <c r="F75" t="n">
+        <v>15.84</v>
+      </c>
+      <c r="G75" t="n">
+        <v>227</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>10.10%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-5</v>
+      </c>
+      <c r="J75" t="n">
+        <v>222</v>
+      </c>
+      <c r="K75" t="n">
+        <v>131</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.4525</v>
+      </c>
+      <c r="N75" t="n">
+        <v>12.57875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.578947368421053</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>4.390000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.3834061135371181</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>3.454545454545454</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.3550042771599657</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
